--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8349514563106796</v>
+        <v>0.8446601941747572</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="D14" t="n">
         <v>0.7946428571428571</v>
       </c>
       <c r="E14" t="n">
-        <v>0.900990099009901</v>
+        <v>0.8712871287128713</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8542955876519419</v>
+        <v>0.846719709956075</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5992424242424242</v>
+        <v>0.6049242424242425</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5619565217391305</v>
+        <v>0.5423913043478261</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6193820224719101</v>
+        <v>0.5304307116104868</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5893760113441354</v>
+        <v>0.5540519492110234</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6130386740331492</v>
+        <v>0.6227106227106227</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6026070763500931</v>
+        <v>0.5380952380952381</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5694467658365369</v>
+        <v>0.54447391688771</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6606182795698925</v>
+        <v>0.5319073083778967</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6114276989474179</v>
+        <v>0.5592967715178668</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8207262779595558</v>
+        <v>0.8278032646964686</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8485016030255909</v>
+        <v>0.8273932253313697</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7696210692199327</v>
+        <v>0.7614879373500063</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8783668689449591</v>
+        <v>0.8357706358871181</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8293039547875096</v>
+        <v>0.8131137658162407</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6814393939393939</v>
+        <v>0.6617424242424244</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6652930402930404</v>
+        <v>0.6973443223443223</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6100543478260869</v>
+        <v>0.5907608695652173</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7120786516853932</v>
+        <v>0.7036516853932585</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6672163584359786</v>
+        <v>0.6633748253863057</v>
       </c>
     </row>
     <row r="19">
@@ -863,27 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[82, 6], [11, 4]]</t>
+          <t>[[83, 5], [11, 4]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[84, 0], [11, 2]]</t>
+          <t>[[84, 0], [12, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[85, 7], [16, 4]]</t>
+          <t>[[86, 6], [17, 3]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[88, 1], [9, 3]]</t>
+          <t>[[87, 2], [11, 1]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[85, 4], [12, 3]]</t>
+          <t>[[85, 3], [13, 2]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8542955876519419</v>
+        <v>0.846719709956075</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04229793999957076</v>
+        <v>0.0323810170588479</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5893760113441354</v>
+        <v>0.5540519492110234</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02182092340606727</v>
+        <v>0.02968579049190035</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6114276989474179</v>
+        <v>0.5592967715178668</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03264395269635605</v>
+        <v>0.03688062246305768</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8293039547875096</v>
+        <v>0.8131137658162407</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04003542997437289</v>
+        <v>0.02999268355628628</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6672163584359786</v>
+        <v>0.6633748253863057</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03703415553300833</v>
+        <v>0.0448653638374913</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[85, 4], [12, 3]]</t>
+          <t>[[85, 3], [13, 2]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6796116504854369</v>
+        <v>0.8252427184466019</v>
       </c>
       <c r="C8" t="n">
         <v>0.7835051546391752</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0.7821782178217822</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7666808985937414</v>
+        <v>0.7852315227268898</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7018939393939394</v>
+        <v>0.7318181818181818</v>
       </c>
       <c r="C9" t="n">
         <v>0.6474358974358975</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7934782608695652</v>
+        <v>0.75</v>
       </c>
       <c r="E9" t="n">
         <v>0.6601123595505618</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7007301143124909</v>
+        <v>0.6973416097011602</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.590728476821192</v>
+        <v>0.6970588235294117</v>
       </c>
       <c r="C10" t="n">
         <v>0.616600790513834</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7425287356321839</v>
+        <v>0.6742833402575821</v>
       </c>
       <c r="E10" t="n">
         <v>0.6109943977591037</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6402131001815784</v>
+        <v>0.6497343380149829</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7259049701022311</v>
+        <v>0.8367218732153056</v>
       </c>
       <c r="C11" t="n">
         <v>0.8017603194653845</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8341543513957308</v>
+        <v>0.7752388865808061</v>
       </c>
       <c r="E11" t="n">
         <v>0.8077280417117343</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7923869206687701</v>
+        <v>0.8053622802433076</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.825</v>
+        <v>0.8121212121212121</v>
       </c>
       <c r="C12" t="n">
         <v>0.7847985347985349</v>
       </c>
       <c r="D12" t="n">
-        <v>0.825</v>
+        <v>0.8423913043478261</v>
       </c>
       <c r="E12" t="n">
         <v>0.7593632958801498</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7985404576696712</v>
+        <v>0.7996685867869308</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[59, 29], [4, 11]]</t>
+          <t>[[76, 12], [6, 9]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[77, 15], [5, 15]]</t>
+          <t>[[69, 23], [5, 15]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[70, 18], [6, 10]]</t>
+          <t>[[72, 16], [6, 9]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7666808985937414</v>
+        <v>0.7852315227268898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05268202763209002</v>
+        <v>0.02671356862249171</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7007301143124909</v>
+        <v>0.6973416097011602</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05721374121000639</v>
+        <v>0.04426662760275556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6402131001815784</v>
+        <v>0.6497343380149829</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0598508373915501</v>
+        <v>0.03688114484852831</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7923869206687701</v>
+        <v>0.8053622802433076</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04027275325986059</v>
+        <v>0.02184842022828315</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7985404576696712</v>
+        <v>0.7996685867869308</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02794595324344613</v>
+        <v>0.0309270649865205</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[70, 18], [6, 10]]</t>
+          <t>[[72, 16], [6, 9]]</t>
         </is>
       </c>
     </row>
